--- a/exports/trend_1d/RADICO_full_report.xlsx
+++ b/exports/trend_1d/RADICO_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q61"/>
+  <dimension ref="A1:U61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>8.32</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42089</v>
+        <v>42090</v>
       </c>
       <c r="H2" t="n">
-        <v>85.15000000000001</v>
+        <v>82.84999999999999</v>
       </c>
       <c r="I2" t="n">
         <v>84.27140970365639</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K2" t="n">
-        <v>1.07</v>
+        <v>-1.66</v>
       </c>
       <c r="L2" t="n">
         <v>2.08</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42033</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>4</v>
+      </c>
+      <c r="U2" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -591,28 +626,28 @@
         <v>16.25</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42104</v>
+        <v>42107</v>
       </c>
       <c r="H3" t="n">
-        <v>94.7</v>
+        <v>99.55</v>
       </c>
       <c r="I3" t="n">
         <v>96.31536953429337</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K3" t="n">
-        <v>-14.3</v>
+        <v>-20.16</v>
       </c>
       <c r="L3" t="n">
-        <v>15.87</v>
+        <v>23.23</v>
       </c>
       <c r="M3" t="n">
         <v>2.39</v>
       </c>
       <c r="N3" t="n">
-        <v>4.95</v>
+        <v>5.12</v>
       </c>
       <c r="O3" t="n">
         <v>-2.7</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42124</v>
+      </c>
+      <c r="S3" t="b">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>14.24</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42153</v>
+        <v>42156</v>
       </c>
       <c r="H4" t="n">
-        <v>86.65000000000001</v>
+        <v>85.95</v>
       </c>
       <c r="I4" t="n">
         <v>86.23302706693752</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="K4" t="n">
-        <v>-12.96</v>
+        <v>-13.66</v>
       </c>
       <c r="L4" t="n">
         <v>14.01</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42124</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>9.609999999999999</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42191</v>
+        <v>42192</v>
       </c>
       <c r="H5" t="n">
-        <v>83</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="I5" t="n">
         <v>87.95775599441613</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K5" t="n">
-        <v>3.43</v>
+        <v>-2.5</v>
       </c>
       <c r="L5" t="n">
         <v>4.25</v>
@@ -726,7 +785,7 @@
         <v>2.33</v>
       </c>
       <c r="N5" t="n">
-        <v>2.73</v>
+        <v>6.14</v>
       </c>
       <c r="O5" t="n">
         <v>-0.8100000000000001</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42180</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>11.99</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>42247</v>
+        <v>42248</v>
       </c>
       <c r="H6" t="n">
-        <v>89.5</v>
+        <v>86.34999999999999</v>
       </c>
       <c r="I6" t="n">
         <v>87.1231911012527</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K6" t="n">
-        <v>1.59</v>
+        <v>-1.99</v>
       </c>
       <c r="L6" t="n">
         <v>7.6</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42215</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>3</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -819,28 +902,28 @@
         <v>18.97</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>42292</v>
+        <v>42293</v>
       </c>
       <c r="H7" t="n">
-        <v>88.59999999999999</v>
+        <v>93.2</v>
       </c>
       <c r="I7" t="n">
         <v>91.74289261633817</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K7" t="n">
-        <v>-2.61</v>
+        <v>-7.93</v>
       </c>
       <c r="L7" t="n">
-        <v>4.63</v>
+        <v>11.52</v>
       </c>
       <c r="M7" t="n">
         <v>2.99</v>
       </c>
       <c r="N7" t="n">
-        <v>4.17</v>
+        <v>5.19</v>
       </c>
       <c r="O7" t="n">
         <v>-3.52</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>42271</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>11.18</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>42346</v>
+        <v>42347</v>
       </c>
       <c r="H8" t="n">
-        <v>104</v>
+        <v>101.35</v>
       </c>
       <c r="I8" t="n">
         <v>103.4564066329785</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K8" t="n">
-        <v>11.59</v>
+        <v>8.74</v>
       </c>
       <c r="L8" t="n">
         <v>4.88</v>
@@ -906,7 +1001,19 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>42306</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>21.26</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>42552</v>
+        <v>42555</v>
       </c>
       <c r="H9" t="n">
-        <v>92.75</v>
+        <v>93.95</v>
       </c>
       <c r="I9" t="n">
         <v>93.18133077998093</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="K9" t="n">
-        <v>8.49</v>
+        <v>7.3</v>
       </c>
       <c r="L9" t="n">
         <v>24.22</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>140</v>
+        <v>141</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>42369</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>8</v>
+      </c>
+      <c r="U9" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>10.95</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>42683</v>
+        <v>42684</v>
       </c>
       <c r="H10" t="n">
-        <v>129.25</v>
+        <v>124.35</v>
       </c>
       <c r="I10" t="n">
         <v>125.0772866223977</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="K10" t="n">
-        <v>37.57</v>
+        <v>32.36</v>
       </c>
       <c r="L10" t="n">
         <v>11.07</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>86</v>
+        <v>87</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>42579</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>5</v>
+      </c>
+      <c r="U10" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>27.67</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>42767</v>
+        <v>42768</v>
       </c>
       <c r="H11" t="n">
-        <v>118.85</v>
+        <v>125</v>
       </c>
       <c r="I11" t="n">
         <v>123.1353675695789</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K11" t="n">
-        <v>4.42</v>
+        <v>-0.52</v>
       </c>
       <c r="L11" t="n">
         <v>9.890000000000001</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>42698</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>4</v>
+      </c>
+      <c r="U11" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -1104,28 +1247,28 @@
         <v>12.84</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>42832</v>
+        <v>42835</v>
       </c>
       <c r="H12" t="n">
-        <v>123.85</v>
+        <v>114.7</v>
       </c>
       <c r="I12" t="n">
         <v>123.2630961291307</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.92</v>
+        <v>-8.24</v>
       </c>
       <c r="L12" t="n">
-        <v>5.08</v>
+        <v>9.6</v>
       </c>
       <c r="M12" t="n">
         <v>2.76</v>
       </c>
       <c r="N12" t="n">
-        <v>3.95</v>
+        <v>7.39</v>
       </c>
       <c r="O12" t="n">
         <v>5.17</v>
@@ -1134,7 +1277,19 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>42789</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>20.86</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>42846</v>
+        <v>42849</v>
       </c>
       <c r="H13" t="n">
-        <v>125.95</v>
+        <v>127.15</v>
       </c>
       <c r="I13" t="n">
         <v>126.1000767616305</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K13" t="n">
-        <v>-9.81</v>
+        <v>-10.85</v>
       </c>
       <c r="L13" t="n">
         <v>15.21</v>
@@ -1191,7 +1346,19 @@
         <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>42852</v>
+      </c>
+      <c r="S13" t="b">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>17.1</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>42999</v>
+        <v>43000</v>
       </c>
       <c r="H14" t="n">
-        <v>165.15</v>
+        <v>156.95</v>
       </c>
       <c r="I14" t="n">
         <v>157.6697533846045</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="K14" t="n">
-        <v>29.89</v>
+        <v>23.44</v>
       </c>
       <c r="L14" t="n">
         <v>11.01</v>
@@ -1239,7 +1406,7 @@
         <v>2.37</v>
       </c>
       <c r="N14" t="n">
-        <v>4.85</v>
+        <v>4.97</v>
       </c>
       <c r="O14" t="n">
         <v>0.95</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>105</v>
+        <v>106</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>42852</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>6</v>
+      </c>
+      <c r="U14" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="15">
@@ -1275,22 +1454,22 @@
         <v>15.06</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>43011</v>
+        <v>43012</v>
       </c>
       <c r="H15" t="n">
-        <v>166.9</v>
+        <v>174.55</v>
       </c>
       <c r="I15" t="n">
         <v>174.0965527995419</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K15" t="n">
-        <v>-6.34</v>
+        <v>-11.21</v>
       </c>
       <c r="L15" t="n">
-        <v>10</v>
+        <v>12.33</v>
       </c>
       <c r="M15" t="n">
         <v>1.07</v>
@@ -1305,7 +1484,19 @@
         <v>1</v>
       </c>
       <c r="Q15" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>43006</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>16.39</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>43132</v>
+        <v>43133</v>
       </c>
       <c r="H16" t="n">
-        <v>351.6</v>
+        <v>324.8</v>
       </c>
       <c r="I16" t="n">
         <v>327.3345017301687</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="K16" t="n">
-        <v>101.43</v>
+        <v>86.08</v>
       </c>
       <c r="L16" t="n">
         <v>4.61</v>
@@ -1362,7 +1553,19 @@
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>83</v>
+        <v>84</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>43034</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>5</v>
+      </c>
+      <c r="U16" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>28.15</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>43194</v>
+        <v>43195</v>
       </c>
       <c r="H17" t="n">
-        <v>354</v>
+        <v>365.3</v>
       </c>
       <c r="I17" t="n">
         <v>365.1029494383491</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K17" t="n">
-        <v>-8.99</v>
+        <v>-12.47</v>
       </c>
       <c r="L17" t="n">
         <v>14.18</v>
@@ -1419,7 +1622,19 @@
         <v>1</v>
       </c>
       <c r="Q17" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>43153</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -1446,25 +1661,25 @@
         <v>13.62</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>43255</v>
+        <v>43256</v>
       </c>
       <c r="H18" t="n">
-        <v>416</v>
+        <v>395.2</v>
       </c>
       <c r="I18" t="n">
         <v>407.8779155618922</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="K18" t="n">
-        <v>13.88</v>
+        <v>8.19</v>
       </c>
       <c r="L18" t="n">
         <v>7.2</v>
       </c>
       <c r="M18" t="n">
-        <v>2.58</v>
+        <v>5</v>
       </c>
       <c r="N18" t="n">
         <v>6.88</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>43216</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>17.73</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>43304</v>
+        <v>43305</v>
       </c>
       <c r="H19" t="n">
-        <v>363.2</v>
+        <v>381.35</v>
       </c>
       <c r="I19" t="n">
         <v>381.0287067503922</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K19" t="n">
-        <v>8.1</v>
+        <v>3.5</v>
       </c>
       <c r="L19" t="n">
         <v>7.3</v>
@@ -1524,7 +1751,7 @@
         <v>2.03</v>
       </c>
       <c r="N19" t="n">
-        <v>4.99</v>
+        <v>5</v>
       </c>
       <c r="O19" t="n">
         <v>-5</v>
@@ -1533,7 +1760,19 @@
         <v>1</v>
       </c>
       <c r="Q19" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>43279</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>16.13</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>43354</v>
+        <v>43355</v>
       </c>
       <c r="H20" t="n">
-        <v>440.85</v>
+        <v>419.15</v>
       </c>
       <c r="I20" t="n">
         <v>428.0384369752844</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K20" t="n">
-        <v>15.6</v>
+        <v>9.91</v>
       </c>
       <c r="L20" t="n">
         <v>4.55</v>
@@ -1590,7 +1829,19 @@
         <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>43307</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>18.78</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>43389</v>
+        <v>43390</v>
       </c>
       <c r="H21" t="n">
-        <v>362.45</v>
+        <v>367.25</v>
       </c>
       <c r="I21" t="n">
         <v>367.2173226158544</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K21" t="n">
-        <v>13.53</v>
+        <v>12.38</v>
       </c>
       <c r="L21" t="n">
         <v>5.44</v>
@@ -1647,7 +1898,19 @@
         <v>1</v>
       </c>
       <c r="Q21" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>43370</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>16.18</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>43439</v>
+        <v>43440</v>
       </c>
       <c r="H22" t="n">
-        <v>392.25</v>
+        <v>378.35</v>
       </c>
       <c r="I22" t="n">
         <v>382.6574777341526</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K22" t="n">
-        <v>6.81</v>
+        <v>3.02</v>
       </c>
       <c r="L22" t="n">
         <v>10.28</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>43398</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>15.3</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>43488</v>
+        <v>43489</v>
       </c>
       <c r="H23" t="n">
-        <v>421.5</v>
+        <v>427.95</v>
       </c>
       <c r="I23" t="n">
         <v>425.9505537086</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K23" t="n">
-        <v>-11.4</v>
+        <v>-13.11</v>
       </c>
       <c r="L23" t="n">
         <v>15.49</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>43461</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,22 +2075,22 @@
         <v>10.51</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>43510</v>
+        <v>43511</v>
       </c>
       <c r="H24" t="n">
-        <v>405.55</v>
+        <v>397.4</v>
       </c>
       <c r="I24" t="n">
         <v>398.6220881083586</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K24" t="n">
-        <v>-5.23</v>
+        <v>-7.14</v>
       </c>
       <c r="L24" t="n">
-        <v>6.3</v>
+        <v>7.5</v>
       </c>
       <c r="M24" t="n">
         <v>1.73</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>43496</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1845,22 +2144,22 @@
         <v>12.34</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>43543</v>
+        <v>43544</v>
       </c>
       <c r="H25" t="n">
-        <v>399.75</v>
+        <v>409.95</v>
       </c>
       <c r="I25" t="n">
         <v>408.9508913674457</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.59</v>
+        <v>-3.16</v>
       </c>
       <c r="L25" t="n">
-        <v>2.86</v>
+        <v>4.08</v>
       </c>
       <c r="M25" t="n">
         <v>1.83</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>43524</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,28 +2213,28 @@
         <v>11.78</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>43566</v>
+        <v>43567</v>
       </c>
       <c r="H26" t="n">
-        <v>369.65</v>
+        <v>357.95</v>
       </c>
       <c r="I26" t="n">
         <v>366.8121703585379</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K26" t="n">
-        <v>-9.83</v>
+        <v>-12.68</v>
       </c>
       <c r="L26" t="n">
-        <v>10.48</v>
+        <v>13.7</v>
       </c>
       <c r="M26" t="n">
         <v>0.89</v>
       </c>
       <c r="N26" t="n">
-        <v>2.86</v>
+        <v>3.17</v>
       </c>
       <c r="O26" t="n">
         <v>2.55</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>43552</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>11.62</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>43641</v>
+        <v>43642</v>
       </c>
       <c r="H27" t="n">
-        <v>295.4</v>
+        <v>311.3</v>
       </c>
       <c r="I27" t="n">
         <v>307.9636027078564</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="K27" t="n">
-        <v>17.47</v>
+        <v>13.03</v>
       </c>
       <c r="L27" t="n">
         <v>6.31</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>43580</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>3</v>
+      </c>
+      <c r="U27" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>15.38</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>43817</v>
+        <v>43818</v>
       </c>
       <c r="H28" t="n">
-        <v>300.65</v>
+        <v>296</v>
       </c>
       <c r="I28" t="n">
         <v>296.0457406900099</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="K28" t="n">
-        <v>-3.42</v>
+        <v>-4.91</v>
       </c>
       <c r="L28" t="n">
         <v>11.28</v>
@@ -2046,7 +2381,19 @@
         <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>118</v>
+        <v>119</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>43643</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>7</v>
+      </c>
+      <c r="U28" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="29">
@@ -2073,22 +2420,22 @@
         <v>8.720000000000001</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>43831</v>
+        <v>43832</v>
       </c>
       <c r="H29" t="n">
-        <v>320.9</v>
+        <v>325.45</v>
       </c>
       <c r="I29" t="n">
         <v>321.2868374198322</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K29" t="n">
-        <v>-8.41</v>
+        <v>-9.949999999999999</v>
       </c>
       <c r="L29" t="n">
-        <v>9.359999999999999</v>
+        <v>11.49</v>
       </c>
       <c r="M29" t="n">
         <v>0.6899999999999999</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>43825</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2130,25 +2489,25 @@
         <v>8.539999999999999</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>43895</v>
+        <v>43896</v>
       </c>
       <c r="H30" t="n">
-        <v>382.75</v>
+        <v>367.8</v>
       </c>
       <c r="I30" t="n">
         <v>377.5528324895768</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K30" t="n">
-        <v>17.61</v>
+        <v>13.01</v>
       </c>
       <c r="L30" t="n">
         <v>6.59</v>
       </c>
       <c r="M30" t="n">
-        <v>2.99</v>
+        <v>3.2</v>
       </c>
       <c r="N30" t="n">
         <v>4.43</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>43860</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>3</v>
+      </c>
+      <c r="U30" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>17.34</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>43987</v>
+        <v>43990</v>
       </c>
       <c r="H31" t="n">
-        <v>345.8</v>
+        <v>351.05</v>
       </c>
       <c r="I31" t="n">
         <v>346.8938408365605</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="K31" t="n">
-        <v>5.98</v>
+        <v>4.55</v>
       </c>
       <c r="L31" t="n">
         <v>1.69</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>43916</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>4</v>
+      </c>
+      <c r="U31" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>11.13</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>44043</v>
+        <v>44046</v>
       </c>
       <c r="H32" t="n">
-        <v>368.5</v>
+        <v>363.1</v>
       </c>
       <c r="I32" t="n">
         <v>365.6623886121899</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="K32" t="n">
-        <v>4.97</v>
+        <v>3.43</v>
       </c>
       <c r="L32" t="n">
         <v>8.289999999999999</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>44007</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>3</v>
+      </c>
+      <c r="U32" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>12.2</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>44064</v>
+        <v>44067</v>
       </c>
       <c r="H33" t="n">
-        <v>403.6</v>
+        <v>408.15</v>
       </c>
       <c r="I33" t="n">
         <v>407.3819127479323</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="K33" t="n">
-        <v>-11.15</v>
+        <v>-12.41</v>
       </c>
       <c r="L33" t="n">
         <v>14.29</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>44070</v>
+      </c>
+      <c r="S33" t="b">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>10.05</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>44097</v>
+        <v>44098</v>
       </c>
       <c r="H34" t="n">
-        <v>414.05</v>
+        <v>397.8</v>
       </c>
       <c r="I34" t="n">
         <v>397.8800549605264</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K34" t="n">
-        <v>1.45</v>
+        <v>-2.54</v>
       </c>
       <c r="L34" t="n">
         <v>7.78</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>44070</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>18.82</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>44145</v>
+        <v>44146</v>
       </c>
       <c r="H35" t="n">
-        <v>458.75</v>
+        <v>462.7</v>
       </c>
       <c r="I35" t="n">
         <v>460.7375824065764</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K35" t="n">
-        <v>-15.32</v>
+        <v>-16.31</v>
       </c>
       <c r="L35" t="n">
         <v>18.59</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>44133</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>13.27</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>44272</v>
+        <v>44273</v>
       </c>
       <c r="H36" t="n">
-        <v>543.8</v>
+        <v>538.85</v>
       </c>
       <c r="I36" t="n">
         <v>542.9545787626799</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="K36" t="n">
-        <v>17.53</v>
+        <v>16.46</v>
       </c>
       <c r="L36" t="n">
         <v>8.800000000000001</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>87</v>
+        <v>88</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>44161</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>5</v>
+      </c>
+      <c r="U36" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>17</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>44314</v>
+        <v>44315</v>
       </c>
       <c r="H37" t="n">
-        <v>566.95</v>
+        <v>574.55</v>
       </c>
       <c r="I37" t="n">
         <v>567.4811918128718</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K37" t="n">
-        <v>-5.21</v>
+        <v>-6.63</v>
       </c>
       <c r="L37" t="n">
         <v>7.14</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>44280</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>10.76</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>44582</v>
+        <v>44585</v>
       </c>
       <c r="H38" t="n">
-        <v>1114.7</v>
+        <v>1047.9</v>
       </c>
       <c r="I38" t="n">
         <v>1111.755062791076</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="K38" t="n">
-        <v>94.01000000000001</v>
+        <v>82.39</v>
       </c>
       <c r="L38" t="n">
         <v>6.52</v>
@@ -2607,7 +3062,7 @@
         <v>3.69</v>
       </c>
       <c r="N38" t="n">
-        <v>4.7</v>
+        <v>5.99</v>
       </c>
       <c r="O38" t="n">
         <v>1.34</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>185</v>
+        <v>186</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>44343</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>9</v>
+      </c>
+      <c r="U38" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>16.91</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>44740</v>
+        <v>44741</v>
       </c>
       <c r="H39" t="n">
-        <v>834.4</v>
+        <v>860.65</v>
       </c>
       <c r="I39" t="n">
         <v>853.1956067919435</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="K39" t="n">
-        <v>20.37</v>
+        <v>17.87</v>
       </c>
       <c r="L39" t="n">
         <v>8.31</v>
@@ -2673,7 +3140,19 @@
         <v>1</v>
       </c>
       <c r="Q39" t="n">
-        <v>106</v>
+        <v>107</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>6</v>
+      </c>
+      <c r="U39" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>12.63</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>44874</v>
+        <v>44875</v>
       </c>
       <c r="H40" t="n">
-        <v>1041.55</v>
+        <v>1008.15</v>
       </c>
       <c r="I40" t="n">
         <v>1009.438255778106</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="K40" t="n">
-        <v>21.02</v>
+        <v>17.14</v>
       </c>
       <c r="L40" t="n">
         <v>4.91</v>
@@ -2721,7 +3200,7 @@
         <v>3.99</v>
       </c>
       <c r="N40" t="n">
-        <v>2.84</v>
+        <v>3.21</v>
       </c>
       <c r="O40" t="n">
         <v>3.15</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>90</v>
+        <v>91</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>6</v>
+      </c>
+      <c r="U40" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="41">
@@ -2757,22 +3248,22 @@
         <v>12.35</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>44890</v>
+        <v>44893</v>
       </c>
       <c r="H41" t="n">
-        <v>1051.1</v>
+        <v>1066</v>
       </c>
       <c r="I41" t="n">
         <v>1057.189758508326</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K41" t="n">
-        <v>-4.26</v>
+        <v>-5.74</v>
       </c>
       <c r="L41" t="n">
-        <v>5.58</v>
+        <v>6.2</v>
       </c>
       <c r="M41" t="n">
         <v>1.08</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2814,28 +3317,28 @@
         <v>10.37</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>44917</v>
+        <v>44918</v>
       </c>
       <c r="H42" t="n">
-        <v>1021.6</v>
+        <v>977.85</v>
       </c>
       <c r="I42" t="n">
         <v>1002.279724210113</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K42" t="n">
-        <v>-4.17</v>
+        <v>-8.27</v>
       </c>
       <c r="L42" t="n">
-        <v>8.16</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="M42" t="n">
-        <v>0.83</v>
+        <v>2.11</v>
       </c>
       <c r="N42" t="n">
-        <v>2.5</v>
+        <v>4.28</v>
       </c>
       <c r="O42" t="n">
         <v>1.42</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S42" t="b">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>1</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -2871,22 +3386,22 @@
         <v>12.55</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>44942</v>
+        <v>44943</v>
       </c>
       <c r="H43" t="n">
-        <v>1069.65</v>
+        <v>1099.65</v>
       </c>
       <c r="I43" t="n">
         <v>1094.121020521881</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K43" t="n">
-        <v>-9.390000000000001</v>
+        <v>-12.46</v>
       </c>
       <c r="L43" t="n">
-        <v>11.16</v>
+        <v>14.12</v>
       </c>
       <c r="M43" t="n">
         <v>1.27</v>
@@ -2901,7 +3416,19 @@
         <v>1</v>
       </c>
       <c r="Q43" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>9.32</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45026</v>
+        <v>45027</v>
       </c>
       <c r="H44" t="n">
-        <v>1111.15</v>
+        <v>1079.35</v>
       </c>
       <c r="I44" t="n">
         <v>1104.058482050417</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K44" t="n">
-        <v>1.05</v>
+        <v>-1.85</v>
       </c>
       <c r="L44" t="n">
         <v>6.74</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>4</v>
+      </c>
+      <c r="U44" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="45">
@@ -2985,22 +3524,22 @@
         <v>13.76</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45078</v>
+        <v>45079</v>
       </c>
       <c r="H45" t="n">
-        <v>1173.1</v>
+        <v>1197.6</v>
       </c>
       <c r="I45" t="n">
         <v>1185.892979065224</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K45" t="n">
-        <v>-8.69</v>
+        <v>-10.96</v>
       </c>
       <c r="L45" t="n">
-        <v>10.44</v>
+        <v>11.18</v>
       </c>
       <c r="M45" t="n">
         <v>0.65</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>3</v>
+      </c>
+      <c r="U45" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>8.5</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45152</v>
+        <v>45154</v>
       </c>
       <c r="H46" t="n">
-        <v>1336.45</v>
+        <v>1297.4</v>
       </c>
       <c r="I46" t="n">
         <v>1312.514168687816</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="K46" t="n">
-        <v>11.59</v>
+        <v>8.33</v>
       </c>
       <c r="L46" t="n">
         <v>2.28</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>3</v>
+      </c>
+      <c r="U46" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="47">
@@ -3099,22 +3662,22 @@
         <v>13.36</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45232</v>
+        <v>45233</v>
       </c>
       <c r="H47" t="n">
-        <v>1279.25</v>
+        <v>1320.2</v>
       </c>
       <c r="I47" t="n">
         <v>1287.575536138831</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K47" t="n">
-        <v>1.4</v>
+        <v>-1.76</v>
       </c>
       <c r="L47" t="n">
-        <v>3.01</v>
+        <v>3.59</v>
       </c>
       <c r="M47" t="n">
         <v>1.28</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>4</v>
+      </c>
+      <c r="U47" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>10.08</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="H48" t="n">
-        <v>1599.3</v>
+        <v>1569.8</v>
       </c>
       <c r="I48" t="n">
         <v>1582.433135815963</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="K48" t="n">
-        <v>21.14</v>
+        <v>18.91</v>
       </c>
       <c r="L48" t="n">
         <v>2.13</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>81</v>
+        <v>82</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>4</v>
+      </c>
+      <c r="U48" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="49">
@@ -3213,22 +3800,22 @@
         <v>9.49</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45373</v>
+        <v>45377</v>
       </c>
       <c r="H49" t="n">
-        <v>1643.3</v>
+        <v>1674</v>
       </c>
       <c r="I49" t="n">
         <v>1655.083313070221</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="K49" t="n">
-        <v>-4.68</v>
+        <v>-6.64</v>
       </c>
       <c r="L49" t="n">
-        <v>6.7</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="M49" t="n">
         <v>1.5</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S49" t="b">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
+        <v>1</v>
+      </c>
+      <c r="U49" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -3270,22 +3869,22 @@
         <v>11.39</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45441</v>
+        <v>45442</v>
       </c>
       <c r="H50" t="n">
-        <v>1609.7</v>
+        <v>1580</v>
       </c>
       <c r="I50" t="n">
         <v>1605.028283664722</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K50" t="n">
-        <v>-3.84</v>
+        <v>-5.62</v>
       </c>
       <c r="L50" t="n">
-        <v>4.83</v>
+        <v>6.09</v>
       </c>
       <c r="M50" t="n">
         <v>1.26</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>3</v>
+      </c>
+      <c r="U50" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>10.34</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45454</v>
+        <v>45455</v>
       </c>
       <c r="H51" t="n">
-        <v>1687.15</v>
+        <v>1720.95</v>
       </c>
       <c r="I51" t="n">
         <v>1718.759570088366</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K51" t="n">
-        <v>-6.78</v>
+        <v>-8.92</v>
       </c>
       <c r="L51" t="n">
         <v>10</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S51" t="b">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>1</v>
+      </c>
+      <c r="U51" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -3384,28 +4007,28 @@
         <v>11.45</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45478</v>
+        <v>45481</v>
       </c>
       <c r="H52" t="n">
-        <v>1716.25</v>
+        <v>1639</v>
       </c>
       <c r="I52" t="n">
         <v>1657.753960306039</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="K52" t="n">
-        <v>-0.27</v>
+        <v>-4.76</v>
       </c>
       <c r="L52" t="n">
-        <v>2.38</v>
+        <v>4.94</v>
       </c>
       <c r="M52" t="n">
         <v>1</v>
       </c>
       <c r="N52" t="n">
-        <v>1.78</v>
+        <v>4.5</v>
       </c>
       <c r="O52" t="n">
         <v>2</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -3441,28 +4076,28 @@
         <v>12.27</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45526</v>
+        <v>45527</v>
       </c>
       <c r="H53" t="n">
-        <v>1765.25</v>
+        <v>1844.45</v>
       </c>
       <c r="I53" t="n">
         <v>1793.646760306071</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K53" t="n">
-        <v>-7.7</v>
+        <v>-12.54</v>
       </c>
       <c r="L53" t="n">
-        <v>9.58</v>
+        <v>13.3</v>
       </c>
       <c r="M53" t="n">
         <v>5.28</v>
       </c>
       <c r="N53" t="n">
-        <v>2.33</v>
+        <v>4.49</v>
       </c>
       <c r="O53" t="n">
         <v>-4.5</v>
@@ -3471,7 +4106,19 @@
         <v>1</v>
       </c>
       <c r="Q53" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>10.49</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45569</v>
+        <v>45572</v>
       </c>
       <c r="H54" t="n">
-        <v>2030.55</v>
+        <v>2007.15</v>
       </c>
       <c r="I54" t="n">
         <v>2016.810537404011</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="K54" t="n">
-        <v>10.09</v>
+        <v>8.82</v>
       </c>
       <c r="L54" t="n">
         <v>4.27</v>
@@ -3528,7 +4175,19 @@
         <v>1</v>
       </c>
       <c r="Q54" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>3</v>
+      </c>
+      <c r="U54" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="55">
@@ -3555,22 +4214,22 @@
         <v>11.35</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45580</v>
+        <v>45581</v>
       </c>
       <c r="H55" t="n">
-        <v>2214.4</v>
+        <v>2219.85</v>
       </c>
       <c r="I55" t="n">
         <v>2217.129891550519</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K55" t="n">
-        <v>-10.33</v>
+        <v>-10.6</v>
       </c>
       <c r="L55" t="n">
-        <v>13.29</v>
+        <v>13.59</v>
       </c>
       <c r="M55" t="n">
         <v>1.12</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S55" t="b">
+        <v>0</v>
+      </c>
+      <c r="T55" t="n">
+        <v>1</v>
+      </c>
+      <c r="U55" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>12.38</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45666</v>
+        <v>45667</v>
       </c>
       <c r="H56" t="n">
-        <v>2388.3</v>
+        <v>2280.9</v>
       </c>
       <c r="I56" t="n">
         <v>2378.282598036003</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K56" t="n">
-        <v>7.59</v>
+        <v>2.75</v>
       </c>
       <c r="L56" t="n">
         <v>6.16</v>
@@ -3633,7 +4304,7 @@
         <v>1.52</v>
       </c>
       <c r="N56" t="n">
-        <v>3.41</v>
+        <v>4.5</v>
       </c>
       <c r="O56" t="n">
         <v>0.25</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>4</v>
+      </c>
+      <c r="U56" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="57">
@@ -3669,19 +4352,19 @@
         <v>13.5</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45733</v>
+        <v>45734</v>
       </c>
       <c r="H57" t="n">
-        <v>2214.35</v>
+        <v>2247.8</v>
       </c>
       <c r="I57" t="n">
         <v>2228.355741010372</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="K57" t="n">
-        <v>2.92</v>
+        <v>1.45</v>
       </c>
       <c r="L57" t="n">
         <v>5.57</v>
@@ -3699,7 +4382,19 @@
         <v>1</v>
       </c>
       <c r="Q57" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>3</v>
+      </c>
+      <c r="U57" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>11.64</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="H58" t="n">
-        <v>3169.3</v>
+        <v>3068.7</v>
       </c>
       <c r="I58" t="n">
         <v>3101.494079555941</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="K58" t="n">
-        <v>41</v>
+        <v>36.52</v>
       </c>
       <c r="L58" t="n">
         <v>2.13</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>186</v>
+        <v>187</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>10</v>
+      </c>
+      <c r="U58" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="59">
@@ -3783,19 +4490,19 @@
         <v>10.95</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46091</v>
+        <v>46092</v>
       </c>
       <c r="H59" t="n">
-        <v>2762.5</v>
+        <v>2894</v>
       </c>
       <c r="I59" t="n">
         <v>2796.106590569723</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K59" t="n">
-        <v>9.98</v>
+        <v>5.69</v>
       </c>
       <c r="L59" t="n">
         <v>10.76</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>4</v>
+      </c>
+      <c r="U59" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="60">
@@ -3840,19 +4559,19 @@
         <v>13.54</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="H60" t="n">
-        <v>4460</v>
+        <v>4368.1</v>
       </c>
       <c r="I60" t="n">
         <v>4401.076032211782</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="K60" t="n">
-        <v>54.11</v>
+        <v>50.94</v>
       </c>
       <c r="L60" t="n">
         <v>11.8</v>
@@ -3870,7 +4589,19 @@
         <v>1</v>
       </c>
       <c r="Q60" t="n">
-        <v>125</v>
+        <v>126</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>7</v>
+      </c>
+      <c r="U60" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="61">
@@ -3921,6 +4652,14 @@
       <c r="Q61" t="n">
         <v>31</v>
       </c>
+      <c r="R61" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="inlineStr"/>
+      <c r="U61" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8879,7 +9618,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>70.7</v>
+        <v>72.2</v>
       </c>
     </row>
     <row r="6">
@@ -8889,7 +9628,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="7">
@@ -8899,7 +9638,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="8">
@@ -8909,7 +9648,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9">
@@ -8919,7 +9658,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="10">
@@ -8929,7 +9668,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="11">
@@ -8939,7 +9678,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="12">
@@ -8949,7 +9688,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="13">
@@ -8959,7 +9698,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>25.4</v>
+        <v>23.7</v>
       </c>
     </row>
     <row r="14">
@@ -8969,7 +9708,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>7.32</v>
+        <v>3.83</v>
       </c>
     </row>
     <row r="15">
@@ -8979,7 +9718,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>16.07</v>
+        <v>11.9</v>
       </c>
     </row>
     <row r="16">
@@ -8989,7 +9728,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-1.72</v>
+        <v>-4.52</v>
       </c>
     </row>
     <row r="17">
@@ -8999,7 +9738,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>101.43</v>
+        <v>86.08</v>
       </c>
     </row>
     <row r="18">
@@ -9009,7 +9748,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>55.9</v>
+        <v>44.1</v>
       </c>
     </row>
     <row r="19">
@@ -9019,7 +9758,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>8.23</v>
+        <v>8.98</v>
       </c>
     </row>
     <row r="20">
@@ -9029,7 +9768,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>7.3</v>
+        <v>8.289999999999999</v>
       </c>
     </row>
     <row r="21">
@@ -9049,7 +9788,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="23">
@@ -9059,7 +9798,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="24">
@@ -9069,7 +9808,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.7</v>
+        <v>2.77</v>
       </c>
     </row>
     <row r="25">
@@ -9089,7 +9828,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>5.42</v>
+        <v>5.72</v>
       </c>
     </row>
     <row r="27">
@@ -9109,7 +9848,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="29">
